--- a/test_support/fixtures/xlsx/xlsx-date-time.xlsx
+++ b/test_support/fixtures/xlsx/xlsx-date-time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Word Project\test_support\fixtures\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBAF90C-E373-4CAA-BE24-EB686FA0B8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E75F155-BDB1-4E5D-AA73-01DAE7F588F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -348,7 +348,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
